--- a/storage/app/public/templates/monthly-report.xlsx
+++ b/storage/app/public/templates/monthly-report.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zain\Desktop\larapel\hse-sistem\storage\app\public\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zain\Desktop\larapel\hse-sistem\public\storage\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C42FA820-B6D1-4D18-8C8C-1A53896F83DA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B34FA8B-41D9-4F92-B067-0C5C3191B7A9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="8130" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="8130" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Summary" sheetId="1" r:id="rId1"/>
@@ -246,13 +246,7 @@
     <t>Kecelakaan</t>
   </si>
   <si>
-    <t>C7</t>
-  </si>
-  <si>
     <t>Reward</t>
-  </si>
-  <si>
-    <t>C8</t>
   </si>
   <si>
     <t>Punishment</t>
@@ -362,6 +356,12 @@
   </si>
   <si>
     <t>Halaman 1 dari 4</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>C4</t>
   </si>
 </sst>
 </file>
@@ -947,123 +947,234 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1082,117 +1193,6 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1205,6 +1205,12 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1225,12 +1231,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1770,206 +1770,206 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="81"/>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81" t="s">
+      <c r="A1" s="89"/>
+      <c r="B1" s="89"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81" t="s">
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
+      <c r="H1" s="89"/>
+      <c r="I1" s="89"/>
+      <c r="J1" s="89"/>
+      <c r="K1" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="81"/>
-      <c r="M1" s="81" t="s">
+      <c r="L1" s="89"/>
+      <c r="M1" s="89" t="s">
         <v>2</v>
       </c>
-      <c r="N1" s="81"/>
+      <c r="N1" s="89"/>
     </row>
     <row r="2" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="81"/>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="82" t="s">
+      <c r="A2" s="89"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="84"/>
-      <c r="K2" s="81" t="s">
+      <c r="E2" s="91"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="91"/>
+      <c r="H2" s="91"/>
+      <c r="I2" s="91"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="89" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
+      <c r="L2" s="89"/>
+      <c r="M2" s="89"/>
+      <c r="N2" s="89"/>
     </row>
     <row r="3" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="81"/>
-      <c r="B3" s="81"/>
-      <c r="C3" s="81"/>
-      <c r="D3" s="85"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="86"/>
-      <c r="I3" s="86"/>
-      <c r="J3" s="87"/>
-      <c r="K3" s="81" t="s">
+      <c r="A3" s="89"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="94"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="94"/>
+      <c r="I3" s="94"/>
+      <c r="J3" s="95"/>
+      <c r="K3" s="89" t="s">
         <v>5</v>
       </c>
-      <c r="L3" s="81"/>
-      <c r="M3" s="81"/>
-      <c r="N3" s="81"/>
+      <c r="L3" s="89"/>
+      <c r="M3" s="89"/>
+      <c r="N3" s="89"/>
     </row>
     <row r="4" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="81"/>
-      <c r="B4" s="81"/>
-      <c r="C4" s="81"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="86"/>
-      <c r="H4" s="86"/>
-      <c r="I4" s="86"/>
-      <c r="J4" s="87"/>
-      <c r="K4" s="88" t="s">
-        <v>93</v>
-      </c>
-      <c r="L4" s="89"/>
-      <c r="M4" s="89"/>
-      <c r="N4" s="90"/>
+      <c r="A4" s="89"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="93"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="94"/>
+      <c r="G4" s="94"/>
+      <c r="H4" s="94"/>
+      <c r="I4" s="94"/>
+      <c r="J4" s="95"/>
+      <c r="K4" s="96" t="s">
+        <v>91</v>
+      </c>
+      <c r="L4" s="97"/>
+      <c r="M4" s="97"/>
+      <c r="N4" s="98"/>
     </row>
     <row r="5" spans="1:14" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="81"/>
-      <c r="B5" s="81"/>
-      <c r="C5" s="81"/>
+      <c r="A5" s="89"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
       <c r="D5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="94" t="s">
+      <c r="E5" s="102" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="94"/>
-      <c r="G5" s="94"/>
-      <c r="H5" s="94" t="s">
+      <c r="F5" s="102"/>
+      <c r="G5" s="102"/>
+      <c r="H5" s="102" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="94"/>
-      <c r="J5" s="94"/>
-      <c r="K5" s="91"/>
-      <c r="L5" s="92"/>
-      <c r="M5" s="92"/>
-      <c r="N5" s="93"/>
+      <c r="I5" s="102"/>
+      <c r="J5" s="102"/>
+      <c r="K5" s="99"/>
+      <c r="L5" s="100"/>
+      <c r="M5" s="100"/>
+      <c r="N5" s="101"/>
     </row>
     <row r="7" spans="1:14" s="57" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="95" t="s">
+      <c r="B7" s="82" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="95"/>
-      <c r="D7" s="95"/>
-      <c r="E7" s="95"/>
-      <c r="F7" s="95"/>
-      <c r="G7" s="95"/>
-      <c r="H7" s="95"/>
-      <c r="I7" s="95"/>
-      <c r="J7" s="95"/>
-      <c r="K7" s="95"/>
-      <c r="L7" s="95"/>
-      <c r="M7" s="95"/>
-      <c r="N7" s="95"/>
+      <c r="C7" s="82"/>
+      <c r="D7" s="82"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="82"/>
+      <c r="G7" s="82"/>
+      <c r="H7" s="82"/>
+      <c r="I7" s="82"/>
+      <c r="J7" s="82"/>
+      <c r="K7" s="82"/>
+      <c r="L7" s="82"/>
+      <c r="M7" s="82"/>
+      <c r="N7" s="82"/>
     </row>
     <row r="8" spans="1:14" s="57" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="74" t="s">
+      <c r="B8" s="80" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="74"/>
-      <c r="D8" s="74"/>
-      <c r="E8" s="74" t="s">
+      <c r="C8" s="80"/>
+      <c r="D8" s="80"/>
+      <c r="E8" s="80" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="74"/>
-      <c r="G8" s="74"/>
-      <c r="H8" s="74"/>
-      <c r="I8" s="74"/>
-      <c r="J8" s="74"/>
-      <c r="K8" s="74"/>
-      <c r="L8" s="74"/>
-      <c r="M8" s="74"/>
-      <c r="N8" s="74"/>
+      <c r="F8" s="80"/>
+      <c r="G8" s="80"/>
+      <c r="H8" s="80"/>
+      <c r="I8" s="80"/>
+      <c r="J8" s="80"/>
+      <c r="K8" s="80"/>
+      <c r="L8" s="80"/>
+      <c r="M8" s="80"/>
+      <c r="N8" s="80"/>
     </row>
     <row r="9" spans="1:14" s="57" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="74" t="s">
+      <c r="B9" s="80" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="74"/>
-      <c r="D9" s="74"/>
-      <c r="E9" s="74"/>
-      <c r="F9" s="74"/>
-      <c r="G9" s="74"/>
-      <c r="H9" s="74"/>
-      <c r="I9" s="74"/>
-      <c r="J9" s="74"/>
-      <c r="K9" s="74"/>
-      <c r="L9" s="74"/>
-      <c r="M9" s="74"/>
-      <c r="N9" s="74"/>
+      <c r="C9" s="80"/>
+      <c r="D9" s="80"/>
+      <c r="E9" s="80"/>
+      <c r="F9" s="80"/>
+      <c r="G9" s="80"/>
+      <c r="H9" s="80"/>
+      <c r="I9" s="80"/>
+      <c r="J9" s="80"/>
+      <c r="K9" s="80"/>
+      <c r="L9" s="80"/>
+      <c r="M9" s="80"/>
+      <c r="N9" s="80"/>
     </row>
     <row r="10" spans="1:14" s="57" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="74" t="s">
+      <c r="B10" s="80" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="74"/>
-      <c r="D10" s="74"/>
-      <c r="E10" s="74"/>
-      <c r="F10" s="74"/>
-      <c r="G10" s="74"/>
-      <c r="H10" s="74"/>
-      <c r="I10" s="74"/>
-      <c r="J10" s="74"/>
-      <c r="K10" s="74"/>
-      <c r="L10" s="74"/>
-      <c r="M10" s="74"/>
-      <c r="N10" s="74"/>
+      <c r="C10" s="80"/>
+      <c r="D10" s="80"/>
+      <c r="E10" s="80"/>
+      <c r="F10" s="80"/>
+      <c r="G10" s="80"/>
+      <c r="H10" s="80"/>
+      <c r="I10" s="80"/>
+      <c r="J10" s="80"/>
+      <c r="K10" s="80"/>
+      <c r="L10" s="80"/>
+      <c r="M10" s="80"/>
+      <c r="N10" s="80"/>
     </row>
     <row r="11" spans="1:14" s="57" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="74" t="s">
+      <c r="B11" s="80" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="74"/>
-      <c r="D11" s="74"/>
-      <c r="E11" s="74"/>
-      <c r="F11" s="74"/>
-      <c r="G11" s="74"/>
-      <c r="H11" s="74"/>
-      <c r="I11" s="74"/>
-      <c r="J11" s="74"/>
-      <c r="K11" s="74"/>
-      <c r="L11" s="74"/>
-      <c r="M11" s="74"/>
-      <c r="N11" s="74"/>
+      <c r="C11" s="80"/>
+      <c r="D11" s="80"/>
+      <c r="E11" s="80"/>
+      <c r="F11" s="80"/>
+      <c r="G11" s="80"/>
+      <c r="H11" s="80"/>
+      <c r="I11" s="80"/>
+      <c r="J11" s="80"/>
+      <c r="K11" s="80"/>
+      <c r="L11" s="80"/>
+      <c r="M11" s="80"/>
+      <c r="N11" s="80"/>
     </row>
     <row r="12" spans="1:14" s="57" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="59"/>
@@ -1978,86 +1978,86 @@
       <c r="D12" s="60"/>
     </row>
     <row r="13" spans="1:14" s="57" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="79" t="s">
+      <c r="A13" s="103" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="74" t="s">
+      <c r="B13" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="74"/>
-      <c r="D13" s="74"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="74"/>
-      <c r="G13" s="74"/>
-      <c r="H13" s="74"/>
-      <c r="I13" s="74"/>
-      <c r="J13" s="74"/>
-      <c r="K13" s="74"/>
-      <c r="L13" s="74"/>
-      <c r="M13" s="74"/>
-      <c r="N13" s="74"/>
+      <c r="C13" s="80"/>
+      <c r="D13" s="80"/>
+      <c r="E13" s="80"/>
+      <c r="F13" s="80"/>
+      <c r="G13" s="80"/>
+      <c r="H13" s="80"/>
+      <c r="I13" s="80"/>
+      <c r="J13" s="80"/>
+      <c r="K13" s="80"/>
+      <c r="L13" s="80"/>
+      <c r="M13" s="80"/>
+      <c r="N13" s="80"/>
     </row>
     <row r="14" spans="1:14" s="57" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="79"/>
-      <c r="B14" s="74" t="s">
+      <c r="A14" s="103"/>
+      <c r="B14" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="74"/>
-      <c r="D14" s="74"/>
-      <c r="E14" s="74" t="s">
+      <c r="C14" s="80"/>
+      <c r="D14" s="80"/>
+      <c r="E14" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="74"/>
-      <c r="G14" s="74"/>
-      <c r="H14" s="74"/>
-      <c r="I14" s="74"/>
-      <c r="J14" s="80" t="s">
+      <c r="F14" s="80"/>
+      <c r="G14" s="80"/>
+      <c r="H14" s="80"/>
+      <c r="I14" s="80"/>
+      <c r="J14" s="104" t="s">
         <v>24</v>
       </c>
-      <c r="K14" s="80"/>
-      <c r="L14" s="80"/>
-      <c r="M14" s="80"/>
-      <c r="N14" s="80"/>
+      <c r="K14" s="104"/>
+      <c r="L14" s="104"/>
+      <c r="M14" s="104"/>
+      <c r="N14" s="104"/>
     </row>
     <row r="15" spans="1:14" s="57" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="79"/>
-      <c r="B15" s="74"/>
-      <c r="C15" s="74"/>
-      <c r="D15" s="74"/>
-      <c r="E15" s="96" t="s">
+      <c r="A15" s="103"/>
+      <c r="B15" s="80"/>
+      <c r="C15" s="80"/>
+      <c r="D15" s="80"/>
+      <c r="E15" s="83" t="s">
         <v>25</v>
       </c>
-      <c r="F15" s="97"/>
-      <c r="G15" s="97"/>
-      <c r="H15" s="97"/>
-      <c r="I15" s="98"/>
-      <c r="J15" s="99" t="s">
+      <c r="F15" s="84"/>
+      <c r="G15" s="84"/>
+      <c r="H15" s="84"/>
+      <c r="I15" s="85"/>
+      <c r="J15" s="86" t="s">
         <v>24</v>
       </c>
-      <c r="K15" s="100"/>
-      <c r="L15" s="100"/>
-      <c r="M15" s="100"/>
-      <c r="N15" s="101"/>
+      <c r="K15" s="87"/>
+      <c r="L15" s="87"/>
+      <c r="M15" s="87"/>
+      <c r="N15" s="88"/>
     </row>
     <row r="16" spans="1:14" s="57" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="79"/>
-      <c r="B16" s="74"/>
-      <c r="C16" s="74"/>
-      <c r="D16" s="74"/>
-      <c r="E16" s="74" t="s">
+      <c r="A16" s="103"/>
+      <c r="B16" s="80"/>
+      <c r="C16" s="80"/>
+      <c r="D16" s="80"/>
+      <c r="E16" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="F16" s="74"/>
-      <c r="G16" s="74"/>
-      <c r="H16" s="74"/>
-      <c r="I16" s="74"/>
-      <c r="J16" s="80" t="s">
+      <c r="F16" s="80"/>
+      <c r="G16" s="80"/>
+      <c r="H16" s="80"/>
+      <c r="I16" s="80"/>
+      <c r="J16" s="104" t="s">
         <v>24</v>
       </c>
-      <c r="K16" s="80"/>
-      <c r="L16" s="80"/>
-      <c r="M16" s="80"/>
-      <c r="N16" s="80"/>
+      <c r="K16" s="104"/>
+      <c r="L16" s="104"/>
+      <c r="M16" s="104"/>
+      <c r="N16" s="104"/>
     </row>
     <row r="17" spans="1:14" s="57" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="59"/>
@@ -2069,315 +2069,315 @@
       <c r="A18" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="76" t="s">
+      <c r="B18" s="105" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="77"/>
-      <c r="D18" s="78"/>
-      <c r="E18" s="76" t="s">
+      <c r="C18" s="106"/>
+      <c r="D18" s="107"/>
+      <c r="E18" s="105" t="s">
         <v>29</v>
       </c>
-      <c r="F18" s="77"/>
-      <c r="G18" s="77"/>
-      <c r="H18" s="77"/>
-      <c r="I18" s="77"/>
-      <c r="J18" s="77"/>
-      <c r="K18" s="77"/>
-      <c r="L18" s="77"/>
-      <c r="M18" s="77"/>
-      <c r="N18" s="78"/>
+      <c r="F18" s="106"/>
+      <c r="G18" s="106"/>
+      <c r="H18" s="106"/>
+      <c r="I18" s="106"/>
+      <c r="J18" s="106"/>
+      <c r="K18" s="106"/>
+      <c r="L18" s="106"/>
+      <c r="M18" s="106"/>
+      <c r="N18" s="107"/>
     </row>
     <row r="19" spans="1:14" s="57" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="74" t="s">
+      <c r="B19" s="80" t="s">
         <v>31</v>
       </c>
-      <c r="C19" s="74"/>
-      <c r="D19" s="74"/>
-      <c r="E19" s="74"/>
-      <c r="F19" s="74"/>
-      <c r="G19" s="74"/>
-      <c r="H19" s="74"/>
-      <c r="I19" s="74"/>
-      <c r="J19" s="74"/>
-      <c r="K19" s="74"/>
-      <c r="L19" s="74"/>
-      <c r="M19" s="74"/>
-      <c r="N19" s="74"/>
+      <c r="C19" s="80"/>
+      <c r="D19" s="80"/>
+      <c r="E19" s="80"/>
+      <c r="F19" s="80"/>
+      <c r="G19" s="80"/>
+      <c r="H19" s="80"/>
+      <c r="I19" s="80"/>
+      <c r="J19" s="80"/>
+      <c r="K19" s="80"/>
+      <c r="L19" s="80"/>
+      <c r="M19" s="80"/>
+      <c r="N19" s="80"/>
     </row>
     <row r="20" spans="1:14" s="57" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="74" t="s">
+      <c r="B20" s="80" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="74"/>
-      <c r="D20" s="74"/>
-      <c r="E20" s="75"/>
-      <c r="F20" s="74"/>
-      <c r="G20" s="74"/>
-      <c r="H20" s="74"/>
-      <c r="I20" s="74"/>
-      <c r="J20" s="74"/>
-      <c r="K20" s="74"/>
-      <c r="L20" s="74"/>
-      <c r="M20" s="74"/>
-      <c r="N20" s="74"/>
+      <c r="C20" s="80"/>
+      <c r="D20" s="80"/>
+      <c r="E20" s="81"/>
+      <c r="F20" s="80"/>
+      <c r="G20" s="80"/>
+      <c r="H20" s="80"/>
+      <c r="I20" s="80"/>
+      <c r="J20" s="80"/>
+      <c r="K20" s="80"/>
+      <c r="L20" s="80"/>
+      <c r="M20" s="80"/>
+      <c r="N20" s="80"/>
     </row>
     <row r="21" spans="1:14" s="51" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58" t="s">
         <v>34</v>
       </c>
-      <c r="B21" s="74" t="s">
+      <c r="B21" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="74"/>
-      <c r="D21" s="74"/>
-      <c r="E21" s="75"/>
-      <c r="F21" s="74"/>
-      <c r="G21" s="74"/>
-      <c r="H21" s="74"/>
-      <c r="I21" s="74"/>
-      <c r="J21" s="74"/>
-      <c r="K21" s="74"/>
-      <c r="L21" s="74"/>
-      <c r="M21" s="74"/>
-      <c r="N21" s="74"/>
+      <c r="C21" s="80"/>
+      <c r="D21" s="80"/>
+      <c r="E21" s="81"/>
+      <c r="F21" s="80"/>
+      <c r="G21" s="80"/>
+      <c r="H21" s="80"/>
+      <c r="I21" s="80"/>
+      <c r="J21" s="80"/>
+      <c r="K21" s="80"/>
+      <c r="L21" s="80"/>
+      <c r="M21" s="80"/>
+      <c r="N21" s="80"/>
     </row>
     <row r="22" spans="1:14" s="51" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="74" t="s">
+      <c r="B22" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="C22" s="74"/>
-      <c r="D22" s="74"/>
-      <c r="E22" s="75"/>
-      <c r="F22" s="74"/>
-      <c r="G22" s="74"/>
-      <c r="H22" s="74"/>
-      <c r="I22" s="74"/>
-      <c r="J22" s="74"/>
-      <c r="K22" s="74"/>
-      <c r="L22" s="74"/>
-      <c r="M22" s="74"/>
-      <c r="N22" s="74"/>
+      <c r="C22" s="80"/>
+      <c r="D22" s="80"/>
+      <c r="E22" s="81"/>
+      <c r="F22" s="80"/>
+      <c r="G22" s="80"/>
+      <c r="H22" s="80"/>
+      <c r="I22" s="80"/>
+      <c r="J22" s="80"/>
+      <c r="K22" s="80"/>
+      <c r="L22" s="80"/>
+      <c r="M22" s="80"/>
+      <c r="N22" s="80"/>
     </row>
     <row r="23" spans="1:14" s="51" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="74" t="s">
+      <c r="B23" s="80" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="74"/>
-      <c r="D23" s="74"/>
-      <c r="E23" s="75"/>
-      <c r="F23" s="74"/>
-      <c r="G23" s="74"/>
-      <c r="H23" s="74"/>
-      <c r="I23" s="74"/>
-      <c r="J23" s="74"/>
-      <c r="K23" s="74"/>
-      <c r="L23" s="74"/>
-      <c r="M23" s="74"/>
-      <c r="N23" s="74"/>
+      <c r="C23" s="80"/>
+      <c r="D23" s="80"/>
+      <c r="E23" s="81"/>
+      <c r="F23" s="80"/>
+      <c r="G23" s="80"/>
+      <c r="H23" s="80"/>
+      <c r="I23" s="80"/>
+      <c r="J23" s="80"/>
+      <c r="K23" s="80"/>
+      <c r="L23" s="80"/>
+      <c r="M23" s="80"/>
+      <c r="N23" s="80"/>
     </row>
     <row r="24" spans="1:14" s="51" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="74" t="s">
+      <c r="B24" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="C24" s="74"/>
-      <c r="D24" s="74"/>
-      <c r="E24" s="75"/>
-      <c r="F24" s="74"/>
-      <c r="G24" s="74"/>
-      <c r="H24" s="74"/>
-      <c r="I24" s="74"/>
-      <c r="J24" s="74"/>
-      <c r="K24" s="74"/>
-      <c r="L24" s="74"/>
-      <c r="M24" s="74"/>
-      <c r="N24" s="74"/>
+      <c r="C24" s="80"/>
+      <c r="D24" s="80"/>
+      <c r="E24" s="81"/>
+      <c r="F24" s="80"/>
+      <c r="G24" s="80"/>
+      <c r="H24" s="80"/>
+      <c r="I24" s="80"/>
+      <c r="J24" s="80"/>
+      <c r="K24" s="80"/>
+      <c r="L24" s="80"/>
+      <c r="M24" s="80"/>
+      <c r="N24" s="80"/>
     </row>
     <row r="25" spans="1:14" s="51" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="74" t="s">
+      <c r="B25" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="C25" s="74"/>
-      <c r="D25" s="74"/>
-      <c r="E25" s="75"/>
-      <c r="F25" s="74"/>
-      <c r="G25" s="74"/>
-      <c r="H25" s="74"/>
-      <c r="I25" s="74"/>
-      <c r="J25" s="74"/>
-      <c r="K25" s="74"/>
-      <c r="L25" s="74"/>
-      <c r="M25" s="74"/>
-      <c r="N25" s="74"/>
+      <c r="C25" s="80"/>
+      <c r="D25" s="80"/>
+      <c r="E25" s="81"/>
+      <c r="F25" s="80"/>
+      <c r="G25" s="80"/>
+      <c r="H25" s="80"/>
+      <c r="I25" s="80"/>
+      <c r="J25" s="80"/>
+      <c r="K25" s="80"/>
+      <c r="L25" s="80"/>
+      <c r="M25" s="80"/>
+      <c r="N25" s="80"/>
     </row>
     <row r="26" spans="1:14" s="51" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="58" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="74" t="s">
+      <c r="B26" s="80" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="74"/>
-      <c r="D26" s="74"/>
-      <c r="E26" s="75"/>
-      <c r="F26" s="74"/>
-      <c r="G26" s="74"/>
-      <c r="H26" s="74"/>
-      <c r="I26" s="74"/>
-      <c r="J26" s="74"/>
-      <c r="K26" s="74"/>
-      <c r="L26" s="74"/>
-      <c r="M26" s="74"/>
-      <c r="N26" s="74"/>
+      <c r="C26" s="80"/>
+      <c r="D26" s="80"/>
+      <c r="E26" s="81"/>
+      <c r="F26" s="80"/>
+      <c r="G26" s="80"/>
+      <c r="H26" s="80"/>
+      <c r="I26" s="80"/>
+      <c r="J26" s="80"/>
+      <c r="K26" s="80"/>
+      <c r="L26" s="80"/>
+      <c r="M26" s="80"/>
+      <c r="N26" s="80"/>
     </row>
     <row r="27" spans="1:14" s="51" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="B27" s="74" t="s">
+      <c r="B27" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="74"/>
-      <c r="D27" s="74"/>
-      <c r="E27" s="75"/>
-      <c r="F27" s="74"/>
-      <c r="G27" s="74"/>
-      <c r="H27" s="74"/>
-      <c r="I27" s="74"/>
-      <c r="J27" s="74"/>
-      <c r="K27" s="74"/>
-      <c r="L27" s="74"/>
-      <c r="M27" s="74"/>
-      <c r="N27" s="74"/>
+      <c r="C27" s="80"/>
+      <c r="D27" s="80"/>
+      <c r="E27" s="81"/>
+      <c r="F27" s="80"/>
+      <c r="G27" s="80"/>
+      <c r="H27" s="80"/>
+      <c r="I27" s="80"/>
+      <c r="J27" s="80"/>
+      <c r="K27" s="80"/>
+      <c r="L27" s="80"/>
+      <c r="M27" s="80"/>
+      <c r="N27" s="80"/>
     </row>
     <row r="28" spans="1:14" s="51" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="102" t="s">
+      <c r="A28" s="72" t="s">
         <v>46</v>
       </c>
-      <c r="B28" s="109" t="s">
+      <c r="B28" s="79" t="s">
         <v>47</v>
       </c>
-      <c r="C28" s="104" t="s">
+      <c r="C28" s="74" t="s">
         <v>48</v>
       </c>
-      <c r="D28" s="105"/>
-      <c r="E28" s="74"/>
-      <c r="F28" s="74"/>
-      <c r="G28" s="74"/>
-      <c r="H28" s="74"/>
-      <c r="I28" s="74"/>
-      <c r="J28" s="74"/>
-      <c r="K28" s="74"/>
-      <c r="L28" s="74"/>
-      <c r="M28" s="74"/>
-      <c r="N28" s="74"/>
+      <c r="D28" s="75"/>
+      <c r="E28" s="80"/>
+      <c r="F28" s="80"/>
+      <c r="G28" s="80"/>
+      <c r="H28" s="80"/>
+      <c r="I28" s="80"/>
+      <c r="J28" s="80"/>
+      <c r="K28" s="80"/>
+      <c r="L28" s="80"/>
+      <c r="M28" s="80"/>
+      <c r="N28" s="80"/>
     </row>
     <row r="29" spans="1:14" s="51" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="103"/>
-      <c r="B29" s="108"/>
-      <c r="C29" s="106" t="s">
+      <c r="A29" s="73"/>
+      <c r="B29" s="78"/>
+      <c r="C29" s="76" t="s">
         <v>49</v>
       </c>
-      <c r="D29" s="107"/>
-      <c r="E29" s="74"/>
-      <c r="F29" s="74"/>
-      <c r="G29" s="74"/>
-      <c r="H29" s="74"/>
-      <c r="I29" s="74"/>
-      <c r="J29" s="74"/>
-      <c r="K29" s="74"/>
-      <c r="L29" s="74"/>
-      <c r="M29" s="74"/>
-      <c r="N29" s="74"/>
+      <c r="D29" s="77"/>
+      <c r="E29" s="80"/>
+      <c r="F29" s="80"/>
+      <c r="G29" s="80"/>
+      <c r="H29" s="80"/>
+      <c r="I29" s="80"/>
+      <c r="J29" s="80"/>
+      <c r="K29" s="80"/>
+      <c r="L29" s="80"/>
+      <c r="M29" s="80"/>
+      <c r="N29" s="80"/>
     </row>
     <row r="30" spans="1:14" s="51" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="103"/>
-      <c r="B30" s="108"/>
-      <c r="C30" s="106" t="s">
+      <c r="A30" s="73"/>
+      <c r="B30" s="78"/>
+      <c r="C30" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="D30" s="107"/>
-      <c r="E30" s="74"/>
-      <c r="F30" s="74"/>
-      <c r="G30" s="74"/>
-      <c r="H30" s="74"/>
-      <c r="I30" s="74"/>
-      <c r="J30" s="74"/>
-      <c r="K30" s="74"/>
-      <c r="L30" s="74"/>
-      <c r="M30" s="74"/>
-      <c r="N30" s="74"/>
+      <c r="D30" s="77"/>
+      <c r="E30" s="80"/>
+      <c r="F30" s="80"/>
+      <c r="G30" s="80"/>
+      <c r="H30" s="80"/>
+      <c r="I30" s="80"/>
+      <c r="J30" s="80"/>
+      <c r="K30" s="80"/>
+      <c r="L30" s="80"/>
+      <c r="M30" s="80"/>
+      <c r="N30" s="80"/>
     </row>
     <row r="31" spans="1:14" s="51" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="103"/>
-      <c r="B31" s="108"/>
-      <c r="C31" s="106" t="s">
+      <c r="A31" s="73"/>
+      <c r="B31" s="78"/>
+      <c r="C31" s="76" t="s">
         <v>51</v>
       </c>
-      <c r="D31" s="107"/>
-      <c r="E31" s="74"/>
-      <c r="F31" s="74"/>
-      <c r="G31" s="74"/>
-      <c r="H31" s="74"/>
-      <c r="I31" s="74"/>
-      <c r="J31" s="74"/>
-      <c r="K31" s="74"/>
-      <c r="L31" s="74"/>
-      <c r="M31" s="74"/>
-      <c r="N31" s="74"/>
+      <c r="D31" s="77"/>
+      <c r="E31" s="80"/>
+      <c r="F31" s="80"/>
+      <c r="G31" s="80"/>
+      <c r="H31" s="80"/>
+      <c r="I31" s="80"/>
+      <c r="J31" s="80"/>
+      <c r="K31" s="80"/>
+      <c r="L31" s="80"/>
+      <c r="M31" s="80"/>
+      <c r="N31" s="80"/>
     </row>
     <row r="32" spans="1:14" s="51" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="103"/>
-      <c r="B32" s="108"/>
-      <c r="C32" s="106" t="s">
+      <c r="A32" s="73"/>
+      <c r="B32" s="78"/>
+      <c r="C32" s="76" t="s">
         <v>52</v>
       </c>
-      <c r="D32" s="107"/>
-      <c r="E32" s="74"/>
-      <c r="F32" s="74"/>
-      <c r="G32" s="74"/>
-      <c r="H32" s="74"/>
-      <c r="I32" s="74"/>
-      <c r="J32" s="74"/>
-      <c r="K32" s="74"/>
-      <c r="L32" s="74"/>
-      <c r="M32" s="74"/>
-      <c r="N32" s="74"/>
+      <c r="D32" s="77"/>
+      <c r="E32" s="80"/>
+      <c r="F32" s="80"/>
+      <c r="G32" s="80"/>
+      <c r="H32" s="80"/>
+      <c r="I32" s="80"/>
+      <c r="J32" s="80"/>
+      <c r="K32" s="80"/>
+      <c r="L32" s="80"/>
+      <c r="M32" s="80"/>
+      <c r="N32" s="80"/>
     </row>
     <row r="33" spans="1:14" s="51" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="103"/>
-      <c r="B33" s="108"/>
-      <c r="C33" s="108" t="s">
+      <c r="A33" s="73"/>
+      <c r="B33" s="78"/>
+      <c r="C33" s="78" t="s">
         <v>53</v>
       </c>
-      <c r="D33" s="108"/>
-      <c r="E33" s="74"/>
-      <c r="F33" s="74"/>
-      <c r="G33" s="74"/>
-      <c r="H33" s="74"/>
-      <c r="I33" s="74"/>
-      <c r="J33" s="74"/>
-      <c r="K33" s="74"/>
-      <c r="L33" s="74"/>
-      <c r="M33" s="74"/>
-      <c r="N33" s="74"/>
+      <c r="D33" s="78"/>
+      <c r="E33" s="80"/>
+      <c r="F33" s="80"/>
+      <c r="G33" s="80"/>
+      <c r="H33" s="80"/>
+      <c r="I33" s="80"/>
+      <c r="J33" s="80"/>
+      <c r="K33" s="80"/>
+      <c r="L33" s="80"/>
+      <c r="M33" s="80"/>
+      <c r="N33" s="80"/>
     </row>
     <row r="34" spans="1:14" s="51" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="11"/>
@@ -2385,8 +2385,8 @@
     <row r="41" spans="1:14" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="11"/>
       <c r="B41" s="11"/>
-      <c r="C41" s="72"/>
-      <c r="D41" s="72"/>
+      <c r="C41" s="108"/>
+      <c r="D41" s="108"/>
     </row>
     <row r="42" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="11"/>
@@ -2419,20 +2419,20 @@
       <c r="K45" s="50"/>
     </row>
     <row r="46" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="73"/>
-      <c r="B46" s="73"/>
-      <c r="C46" s="72"/>
-      <c r="D46" s="72"/>
+      <c r="A46" s="109"/>
+      <c r="B46" s="109"/>
+      <c r="C46" s="108"/>
+      <c r="D46" s="108"/>
       <c r="G46" s="11"/>
       <c r="H46" s="11"/>
-      <c r="I46" s="72"/>
-      <c r="J46" s="72"/>
+      <c r="I46" s="108"/>
+      <c r="J46" s="108"/>
     </row>
     <row r="47" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="73"/>
-      <c r="B47" s="73"/>
-      <c r="C47" s="72"/>
-      <c r="D47" s="72"/>
+      <c r="A47" s="109"/>
+      <c r="B47" s="109"/>
+      <c r="C47" s="108"/>
+      <c r="D47" s="108"/>
       <c r="G47" s="11"/>
       <c r="H47" s="11"/>
       <c r="I47" s="12"/>
@@ -2441,28 +2441,28 @@
     <row r="48" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G48" s="11"/>
       <c r="H48" s="11"/>
-      <c r="I48" s="72"/>
-      <c r="J48" s="72"/>
+      <c r="I48" s="108"/>
+      <c r="J48" s="108"/>
     </row>
     <row r="49" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="73"/>
-      <c r="B49" s="73"/>
-      <c r="C49" s="72"/>
-      <c r="D49" s="72"/>
+      <c r="A49" s="109"/>
+      <c r="B49" s="109"/>
+      <c r="C49" s="108"/>
+      <c r="D49" s="108"/>
       <c r="G49" s="11"/>
       <c r="H49" s="11"/>
       <c r="I49" s="12"/>
       <c r="J49" s="12"/>
     </row>
     <row r="50" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="73"/>
-      <c r="B50" s="73"/>
-      <c r="C50" s="72"/>
-      <c r="D50" s="72"/>
+      <c r="A50" s="109"/>
+      <c r="B50" s="109"/>
+      <c r="C50" s="108"/>
+      <c r="D50" s="108"/>
       <c r="G50" s="11"/>
       <c r="H50" s="11"/>
-      <c r="I50" s="72"/>
-      <c r="J50" s="72"/>
+      <c r="I50" s="108"/>
+      <c r="J50" s="108"/>
     </row>
     <row r="51" spans="1:14" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G51" s="11"/>
@@ -2475,8 +2475,8 @@
       <c r="B52" s="51"/>
       <c r="G52" s="11"/>
       <c r="H52" s="11"/>
-      <c r="I52" s="72"/>
-      <c r="J52" s="72"/>
+      <c r="I52" s="108"/>
+      <c r="J52" s="108"/>
     </row>
     <row r="53" spans="1:14" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="51"/>
@@ -2491,8 +2491,8 @@
       <c r="B54" s="11"/>
       <c r="G54" s="11"/>
       <c r="H54" s="11"/>
-      <c r="I54" s="72"/>
-      <c r="J54" s="72"/>
+      <c r="I54" s="108"/>
+      <c r="J54" s="108"/>
     </row>
     <row r="55" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="51"/>
@@ -2507,8 +2507,8 @@
       <c r="B56" s="51"/>
       <c r="G56" s="11"/>
       <c r="H56" s="11"/>
-      <c r="I56" s="72"/>
-      <c r="J56" s="72"/>
+      <c r="I56" s="108"/>
+      <c r="J56" s="108"/>
     </row>
     <row r="57" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="51"/>
@@ -2900,30 +2900,45 @@
     </row>
   </sheetData>
   <mergeCells count="79">
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="B28:B33"/>
-    <mergeCell ref="E33:N33"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E26:N26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E27:N27"/>
-    <mergeCell ref="E28:N28"/>
-    <mergeCell ref="E29:N29"/>
-    <mergeCell ref="E30:N30"/>
-    <mergeCell ref="E31:N31"/>
-    <mergeCell ref="E32:N32"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:N25"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:N22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:N23"/>
+    <mergeCell ref="I56:J56"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="I54:J54"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="E19:N19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:N20"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E18:N18"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="B13:N13"/>
+    <mergeCell ref="B14:D16"/>
+    <mergeCell ref="E14:I14"/>
+    <mergeCell ref="J14:N14"/>
+    <mergeCell ref="E16:I16"/>
+    <mergeCell ref="J16:N16"/>
+    <mergeCell ref="A1:C5"/>
+    <mergeCell ref="D1:J1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="D2:J4"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="K4:N5"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="H5:J5"/>
     <mergeCell ref="B7:N7"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B21:D21"/>
@@ -2940,45 +2955,30 @@
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="E9:N9"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A1:C5"/>
-    <mergeCell ref="D1:J1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="D2:J4"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="K4:N5"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="A13:A16"/>
-    <mergeCell ref="B13:N13"/>
-    <mergeCell ref="B14:D16"/>
-    <mergeCell ref="E14:I14"/>
-    <mergeCell ref="J14:N14"/>
-    <mergeCell ref="E16:I16"/>
-    <mergeCell ref="J16:N16"/>
-    <mergeCell ref="E19:N19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:N20"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E18:N18"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="I56:J56"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="I46:J46"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="I54:J54"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:N25"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:N22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:N23"/>
+    <mergeCell ref="E33:N33"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:N26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:N27"/>
+    <mergeCell ref="E28:N28"/>
+    <mergeCell ref="E29:N29"/>
+    <mergeCell ref="E30:N30"/>
+    <mergeCell ref="E31:N31"/>
+    <mergeCell ref="E32:N32"/>
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="B28:B33"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.19685039370078999" right="0.19685039370078999" top="0.23622047244093999" bottom="0.23622047244093999" header="0.31496062992126" footer="0.31496062992126"/>
@@ -3009,174 +3009,174 @@
       <c r="E1" s="15"/>
     </row>
     <row r="2" spans="1:35" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="144"/>
-      <c r="B2" s="145"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="127" t="s">
+      <c r="A2" s="129"/>
+      <c r="B2" s="130"/>
+      <c r="C2" s="131"/>
+      <c r="D2" s="116" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="153"/>
-      <c r="F2" s="153"/>
-      <c r="G2" s="153"/>
-      <c r="H2" s="153"/>
-      <c r="I2" s="153"/>
-      <c r="J2" s="153"/>
-      <c r="K2" s="128"/>
-      <c r="L2" s="127" t="s">
+      <c r="E2" s="138"/>
+      <c r="F2" s="138"/>
+      <c r="G2" s="138"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
+      <c r="K2" s="117"/>
+      <c r="L2" s="116" t="s">
         <v>1</v>
       </c>
-      <c r="M2" s="128"/>
-      <c r="N2" s="127"/>
-      <c r="O2" s="128"/>
+      <c r="M2" s="117"/>
+      <c r="N2" s="116"/>
+      <c r="O2" s="117"/>
     </row>
     <row r="3" spans="1:35" s="2" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="147"/>
-      <c r="B3" s="148"/>
-      <c r="C3" s="149"/>
-      <c r="D3" s="82" t="s">
+      <c r="A3" s="132"/>
+      <c r="B3" s="133"/>
+      <c r="C3" s="134"/>
+      <c r="D3" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
-      <c r="K3" s="84"/>
-      <c r="L3" s="127" t="s">
+      <c r="E3" s="91"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="91"/>
+      <c r="H3" s="91"/>
+      <c r="I3" s="91"/>
+      <c r="J3" s="91"/>
+      <c r="K3" s="92"/>
+      <c r="L3" s="116" t="s">
         <v>4</v>
       </c>
-      <c r="M3" s="128"/>
-      <c r="N3" s="127"/>
-      <c r="O3" s="128"/>
+      <c r="M3" s="117"/>
+      <c r="N3" s="116"/>
+      <c r="O3" s="117"/>
     </row>
     <row r="4" spans="1:35" s="2" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="147"/>
-      <c r="B4" s="148"/>
-      <c r="C4" s="149"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="86"/>
-      <c r="H4" s="86"/>
-      <c r="I4" s="86"/>
-      <c r="J4" s="86"/>
-      <c r="K4" s="87"/>
-      <c r="L4" s="127" t="s">
+      <c r="A4" s="132"/>
+      <c r="B4" s="133"/>
+      <c r="C4" s="134"/>
+      <c r="D4" s="93"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="94"/>
+      <c r="G4" s="94"/>
+      <c r="H4" s="94"/>
+      <c r="I4" s="94"/>
+      <c r="J4" s="94"/>
+      <c r="K4" s="95"/>
+      <c r="L4" s="116" t="s">
         <v>5</v>
       </c>
-      <c r="M4" s="128"/>
-      <c r="N4" s="127"/>
-      <c r="O4" s="128"/>
+      <c r="M4" s="117"/>
+      <c r="N4" s="116"/>
+      <c r="O4" s="117"/>
     </row>
     <row r="5" spans="1:35" s="2" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="147"/>
-      <c r="B5" s="148"/>
-      <c r="C5" s="149"/>
-      <c r="D5" s="129"/>
-      <c r="E5" s="130"/>
-      <c r="F5" s="130"/>
-      <c r="G5" s="130"/>
-      <c r="H5" s="130"/>
-      <c r="I5" s="130"/>
-      <c r="J5" s="130"/>
-      <c r="K5" s="131"/>
-      <c r="L5" s="88" t="s">
-        <v>92</v>
-      </c>
-      <c r="M5" s="89"/>
-      <c r="N5" s="89"/>
-      <c r="O5" s="90"/>
+      <c r="A5" s="132"/>
+      <c r="B5" s="133"/>
+      <c r="C5" s="134"/>
+      <c r="D5" s="139"/>
+      <c r="E5" s="140"/>
+      <c r="F5" s="140"/>
+      <c r="G5" s="140"/>
+      <c r="H5" s="140"/>
+      <c r="I5" s="140"/>
+      <c r="J5" s="140"/>
+      <c r="K5" s="141"/>
+      <c r="L5" s="96" t="s">
+        <v>90</v>
+      </c>
+      <c r="M5" s="97"/>
+      <c r="N5" s="97"/>
+      <c r="O5" s="98"/>
     </row>
     <row r="6" spans="1:35" s="2" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="150"/>
-      <c r="B6" s="151"/>
-      <c r="C6" s="152"/>
+      <c r="A6" s="135"/>
+      <c r="B6" s="136"/>
+      <c r="C6" s="137"/>
       <c r="D6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="F6" s="134"/>
-      <c r="G6" s="134"/>
-      <c r="H6" s="135"/>
-      <c r="I6" s="133" t="s">
-        <v>84</v>
-      </c>
-      <c r="J6" s="134"/>
-      <c r="K6" s="135"/>
-      <c r="L6" s="91"/>
-      <c r="M6" s="92"/>
-      <c r="N6" s="92"/>
-      <c r="O6" s="93"/>
+      <c r="E6" s="118" t="s">
+        <v>81</v>
+      </c>
+      <c r="F6" s="119"/>
+      <c r="G6" s="119"/>
+      <c r="H6" s="120"/>
+      <c r="I6" s="118" t="s">
+        <v>82</v>
+      </c>
+      <c r="J6" s="119"/>
+      <c r="K6" s="120"/>
+      <c r="L6" s="99"/>
+      <c r="M6" s="100"/>
+      <c r="N6" s="100"/>
+      <c r="O6" s="101"/>
     </row>
     <row r="7" spans="1:35" s="16" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="17"/>
-      <c r="B7" s="136" t="s">
+      <c r="B7" s="121" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="136"/>
-      <c r="D7" s="136"/>
-      <c r="E7" s="136"/>
-      <c r="F7" s="136"/>
-      <c r="G7" s="136"/>
-      <c r="H7" s="136"/>
-      <c r="I7" s="136"/>
-      <c r="J7" s="136"/>
+      <c r="C7" s="121"/>
+      <c r="D7" s="121"/>
+      <c r="E7" s="121"/>
+      <c r="F7" s="121"/>
+      <c r="G7" s="121"/>
+      <c r="H7" s="121"/>
+      <c r="I7" s="121"/>
+      <c r="J7" s="121"/>
     </row>
     <row r="8" spans="1:35" s="16" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="137" t="s">
+      <c r="A8" s="122" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="137" t="s">
+      <c r="B8" s="122" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="137" t="s">
+      <c r="C8" s="122" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="139" t="s">
+      <c r="D8" s="124" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="141" t="s">
+      <c r="E8" s="126" t="s">
         <v>58</v>
       </c>
-      <c r="F8" s="142"/>
-      <c r="G8" s="142"/>
-      <c r="H8" s="142"/>
-      <c r="I8" s="142"/>
-      <c r="J8" s="142"/>
-      <c r="K8" s="142"/>
-      <c r="L8" s="142"/>
-      <c r="M8" s="142"/>
-      <c r="N8" s="142"/>
-      <c r="O8" s="142"/>
-      <c r="P8" s="142"/>
-      <c r="Q8" s="142"/>
-      <c r="R8" s="142"/>
-      <c r="S8" s="142"/>
-      <c r="T8" s="142"/>
-      <c r="U8" s="142"/>
-      <c r="V8" s="142"/>
-      <c r="W8" s="142"/>
-      <c r="X8" s="142"/>
-      <c r="Y8" s="142"/>
-      <c r="Z8" s="142"/>
-      <c r="AA8" s="142"/>
-      <c r="AB8" s="142"/>
-      <c r="AC8" s="142"/>
-      <c r="AD8" s="142"/>
-      <c r="AE8" s="142"/>
-      <c r="AF8" s="142"/>
-      <c r="AG8" s="142"/>
-      <c r="AH8" s="142"/>
-      <c r="AI8" s="143"/>
+      <c r="F8" s="127"/>
+      <c r="G8" s="127"/>
+      <c r="H8" s="127"/>
+      <c r="I8" s="127"/>
+      <c r="J8" s="127"/>
+      <c r="K8" s="127"/>
+      <c r="L8" s="127"/>
+      <c r="M8" s="127"/>
+      <c r="N8" s="127"/>
+      <c r="O8" s="127"/>
+      <c r="P8" s="127"/>
+      <c r="Q8" s="127"/>
+      <c r="R8" s="127"/>
+      <c r="S8" s="127"/>
+      <c r="T8" s="127"/>
+      <c r="U8" s="127"/>
+      <c r="V8" s="127"/>
+      <c r="W8" s="127"/>
+      <c r="X8" s="127"/>
+      <c r="Y8" s="127"/>
+      <c r="Z8" s="127"/>
+      <c r="AA8" s="127"/>
+      <c r="AB8" s="127"/>
+      <c r="AC8" s="127"/>
+      <c r="AD8" s="127"/>
+      <c r="AE8" s="127"/>
+      <c r="AF8" s="127"/>
+      <c r="AG8" s="127"/>
+      <c r="AH8" s="127"/>
+      <c r="AI8" s="128"/>
     </row>
     <row r="9" spans="1:35" s="16" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="138"/>
-      <c r="B9" s="138"/>
-      <c r="C9" s="138"/>
-      <c r="D9" s="140"/>
+      <c r="A9" s="123"/>
+      <c r="B9" s="123"/>
+      <c r="C9" s="123"/>
+      <c r="D9" s="125"/>
       <c r="E9" s="18">
         <v>1</v>
       </c>
@@ -3309,10 +3309,10 @@
       <c r="AI10" s="21"/>
     </row>
     <row r="11" spans="1:35" s="16" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="123" t="s">
+      <c r="A11" s="143" t="s">
         <v>59</v>
       </c>
-      <c r="B11" s="120" t="s">
+      <c r="B11" s="146" t="s">
         <v>60</v>
       </c>
       <c r="C11" s="22"/>
@@ -3350,8 +3350,8 @@
       <c r="AI11" s="24"/>
     </row>
     <row r="12" spans="1:35" s="16" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="124"/>
-      <c r="B12" s="121"/>
+      <c r="A12" s="144"/>
+      <c r="B12" s="114"/>
       <c r="C12" s="22"/>
       <c r="D12" s="23"/>
       <c r="E12" s="24"/>
@@ -3387,8 +3387,8 @@
       <c r="AI12" s="24"/>
     </row>
     <row r="13" spans="1:35" s="16" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="125"/>
-      <c r="B13" s="122"/>
+      <c r="A13" s="145"/>
+      <c r="B13" s="115"/>
       <c r="C13" s="26" t="s">
         <v>53</v>
       </c>
@@ -3426,47 +3426,47 @@
       <c r="AI13" s="23"/>
     </row>
     <row r="14" spans="1:35" s="16" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="126"/>
-      <c r="B14" s="110"/>
-      <c r="C14" s="110"/>
-      <c r="D14" s="110"/>
-      <c r="E14" s="110"/>
-      <c r="F14" s="110"/>
-      <c r="G14" s="110"/>
-      <c r="H14" s="110"/>
-      <c r="I14" s="110"/>
-      <c r="J14" s="110"/>
-      <c r="K14" s="110"/>
-      <c r="L14" s="110"/>
-      <c r="M14" s="110"/>
-      <c r="N14" s="110"/>
-      <c r="O14" s="110"/>
-      <c r="P14" s="110"/>
-      <c r="Q14" s="110"/>
-      <c r="R14" s="110"/>
-      <c r="S14" s="110"/>
-      <c r="T14" s="110"/>
-      <c r="U14" s="110"/>
-      <c r="V14" s="110"/>
-      <c r="W14" s="110"/>
-      <c r="X14" s="110"/>
-      <c r="Y14" s="110"/>
-      <c r="Z14" s="110"/>
-      <c r="AA14" s="110"/>
-      <c r="AB14" s="110"/>
-      <c r="AC14" s="110"/>
-      <c r="AD14" s="110"/>
-      <c r="AE14" s="110"/>
-      <c r="AF14" s="110"/>
-      <c r="AG14" s="110"/>
-      <c r="AH14" s="110"/>
-      <c r="AI14" s="110"/>
+      <c r="A14" s="147"/>
+      <c r="B14" s="142"/>
+      <c r="C14" s="142"/>
+      <c r="D14" s="142"/>
+      <c r="E14" s="142"/>
+      <c r="F14" s="142"/>
+      <c r="G14" s="142"/>
+      <c r="H14" s="142"/>
+      <c r="I14" s="142"/>
+      <c r="J14" s="142"/>
+      <c r="K14" s="142"/>
+      <c r="L14" s="142"/>
+      <c r="M14" s="142"/>
+      <c r="N14" s="142"/>
+      <c r="O14" s="142"/>
+      <c r="P14" s="142"/>
+      <c r="Q14" s="142"/>
+      <c r="R14" s="142"/>
+      <c r="S14" s="142"/>
+      <c r="T14" s="142"/>
+      <c r="U14" s="142"/>
+      <c r="V14" s="142"/>
+      <c r="W14" s="142"/>
+      <c r="X14" s="142"/>
+      <c r="Y14" s="142"/>
+      <c r="Z14" s="142"/>
+      <c r="AA14" s="142"/>
+      <c r="AB14" s="142"/>
+      <c r="AC14" s="142"/>
+      <c r="AD14" s="142"/>
+      <c r="AE14" s="142"/>
+      <c r="AF14" s="142"/>
+      <c r="AG14" s="142"/>
+      <c r="AH14" s="142"/>
+      <c r="AI14" s="142"/>
     </row>
     <row r="15" spans="1:35" s="16" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="117" t="s">
+      <c r="A15" s="111" t="s">
         <v>61</v>
       </c>
-      <c r="B15" s="120" t="s">
+      <c r="B15" s="146" t="s">
         <v>62</v>
       </c>
       <c r="C15" s="22"/>
@@ -3504,8 +3504,8 @@
       <c r="AI15" s="24"/>
     </row>
     <row r="16" spans="1:35" s="16" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="118"/>
-      <c r="B16" s="121"/>
+      <c r="A16" s="112"/>
+      <c r="B16" s="114"/>
       <c r="C16" s="22"/>
       <c r="D16" s="23"/>
       <c r="E16" s="24"/>
@@ -3541,8 +3541,8 @@
       <c r="AI16" s="24"/>
     </row>
     <row r="17" spans="1:35" s="16" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="119"/>
-      <c r="B17" s="122"/>
+      <c r="A17" s="113"/>
+      <c r="B17" s="115"/>
       <c r="C17" s="26" t="s">
         <v>53</v>
       </c>
@@ -3580,47 +3580,47 @@
       <c r="AI17" s="23"/>
     </row>
     <row r="18" spans="1:35" s="16" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="110"/>
-      <c r="B18" s="110"/>
-      <c r="C18" s="110"/>
-      <c r="D18" s="110"/>
-      <c r="E18" s="110"/>
-      <c r="F18" s="110"/>
-      <c r="G18" s="110"/>
-      <c r="H18" s="110"/>
-      <c r="I18" s="110"/>
-      <c r="J18" s="110"/>
-      <c r="K18" s="110"/>
-      <c r="L18" s="110"/>
-      <c r="M18" s="110"/>
-      <c r="N18" s="110"/>
-      <c r="O18" s="110"/>
-      <c r="P18" s="110"/>
-      <c r="Q18" s="110"/>
-      <c r="R18" s="110"/>
-      <c r="S18" s="110"/>
-      <c r="T18" s="110"/>
-      <c r="U18" s="110"/>
-      <c r="V18" s="110"/>
-      <c r="W18" s="110"/>
-      <c r="X18" s="110"/>
-      <c r="Y18" s="110"/>
-      <c r="Z18" s="110"/>
-      <c r="AA18" s="110"/>
-      <c r="AB18" s="110"/>
-      <c r="AC18" s="110"/>
-      <c r="AD18" s="110"/>
-      <c r="AE18" s="110"/>
-      <c r="AF18" s="110"/>
-      <c r="AG18" s="110"/>
-      <c r="AH18" s="110"/>
-      <c r="AI18" s="110"/>
+      <c r="A18" s="142"/>
+      <c r="B18" s="142"/>
+      <c r="C18" s="142"/>
+      <c r="D18" s="142"/>
+      <c r="E18" s="142"/>
+      <c r="F18" s="142"/>
+      <c r="G18" s="142"/>
+      <c r="H18" s="142"/>
+      <c r="I18" s="142"/>
+      <c r="J18" s="142"/>
+      <c r="K18" s="142"/>
+      <c r="L18" s="142"/>
+      <c r="M18" s="142"/>
+      <c r="N18" s="142"/>
+      <c r="O18" s="142"/>
+      <c r="P18" s="142"/>
+      <c r="Q18" s="142"/>
+      <c r="R18" s="142"/>
+      <c r="S18" s="142"/>
+      <c r="T18" s="142"/>
+      <c r="U18" s="142"/>
+      <c r="V18" s="142"/>
+      <c r="W18" s="142"/>
+      <c r="X18" s="142"/>
+      <c r="Y18" s="142"/>
+      <c r="Z18" s="142"/>
+      <c r="AA18" s="142"/>
+      <c r="AB18" s="142"/>
+      <c r="AC18" s="142"/>
+      <c r="AD18" s="142"/>
+      <c r="AE18" s="142"/>
+      <c r="AF18" s="142"/>
+      <c r="AG18" s="142"/>
+      <c r="AH18" s="142"/>
+      <c r="AI18" s="142"/>
     </row>
     <row r="19" spans="1:35" s="16" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="117" t="s">
-        <v>63</v>
-      </c>
-      <c r="B19" s="121" t="s">
+      <c r="A19" s="111" t="s">
+        <v>92</v>
+      </c>
+      <c r="B19" s="114" t="s">
         <v>64</v>
       </c>
       <c r="C19" s="29"/>
@@ -3658,8 +3658,8 @@
       <c r="AI19" s="27"/>
     </row>
     <row r="20" spans="1:35" s="16" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="118"/>
-      <c r="B20" s="121"/>
+      <c r="A20" s="112"/>
+      <c r="B20" s="114"/>
       <c r="C20" s="29"/>
       <c r="D20" s="61"/>
       <c r="E20" s="27"/>
@@ -3695,8 +3695,8 @@
       <c r="AI20" s="27"/>
     </row>
     <row r="21" spans="1:35" s="16" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="119"/>
-      <c r="B21" s="122"/>
+      <c r="A21" s="113"/>
+      <c r="B21" s="115"/>
       <c r="C21" s="31" t="s">
         <v>53</v>
       </c>
@@ -3771,10 +3771,10 @@
       <c r="AI22" s="55"/>
     </row>
     <row r="23" spans="1:35" s="16" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="117" t="s">
-        <v>65</v>
-      </c>
-      <c r="B23" s="121" t="s">
+      <c r="A23" s="111" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" s="114" t="s">
         <v>66</v>
       </c>
       <c r="C23" s="29"/>
@@ -3812,8 +3812,8 @@
       <c r="AI23" s="27"/>
     </row>
     <row r="24" spans="1:35" s="16" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="118"/>
-      <c r="B24" s="121"/>
+      <c r="A24" s="112"/>
+      <c r="B24" s="114"/>
       <c r="C24" s="29"/>
       <c r="D24" s="61"/>
       <c r="E24" s="27"/>
@@ -3849,8 +3849,8 @@
       <c r="AI24" s="27"/>
     </row>
     <row r="25" spans="1:35" s="16" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="119"/>
-      <c r="B25" s="122"/>
+      <c r="A25" s="113"/>
+      <c r="B25" s="115"/>
       <c r="C25" s="31" t="s">
         <v>53</v>
       </c>
@@ -3888,48 +3888,48 @@
       <c r="AI25" s="23"/>
     </row>
     <row r="26" spans="1:35" s="16" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="110"/>
-      <c r="B26" s="110"/>
-      <c r="C26" s="110"/>
-      <c r="D26" s="110"/>
-      <c r="E26" s="110"/>
-      <c r="F26" s="110"/>
-      <c r="G26" s="110"/>
-      <c r="H26" s="110"/>
-      <c r="I26" s="110"/>
-      <c r="J26" s="110"/>
-      <c r="K26" s="110"/>
-      <c r="L26" s="110"/>
-      <c r="M26" s="110"/>
-      <c r="N26" s="110"/>
-      <c r="O26" s="110"/>
-      <c r="P26" s="110"/>
-      <c r="Q26" s="110"/>
-      <c r="R26" s="110"/>
-      <c r="S26" s="110"/>
-      <c r="T26" s="110"/>
-      <c r="U26" s="110"/>
-      <c r="V26" s="110"/>
-      <c r="W26" s="110"/>
-      <c r="X26" s="110"/>
-      <c r="Y26" s="110"/>
-      <c r="Z26" s="110"/>
-      <c r="AA26" s="110"/>
-      <c r="AB26" s="110"/>
-      <c r="AC26" s="110"/>
-      <c r="AD26" s="110"/>
-      <c r="AE26" s="110"/>
-      <c r="AF26" s="110"/>
-      <c r="AG26" s="110"/>
-      <c r="AH26" s="110"/>
-      <c r="AI26" s="110"/>
+      <c r="A26" s="142"/>
+      <c r="B26" s="142"/>
+      <c r="C26" s="142"/>
+      <c r="D26" s="142"/>
+      <c r="E26" s="142"/>
+      <c r="F26" s="142"/>
+      <c r="G26" s="142"/>
+      <c r="H26" s="142"/>
+      <c r="I26" s="142"/>
+      <c r="J26" s="142"/>
+      <c r="K26" s="142"/>
+      <c r="L26" s="142"/>
+      <c r="M26" s="142"/>
+      <c r="N26" s="142"/>
+      <c r="O26" s="142"/>
+      <c r="P26" s="142"/>
+      <c r="Q26" s="142"/>
+      <c r="R26" s="142"/>
+      <c r="S26" s="142"/>
+      <c r="T26" s="142"/>
+      <c r="U26" s="142"/>
+      <c r="V26" s="142"/>
+      <c r="W26" s="142"/>
+      <c r="X26" s="142"/>
+      <c r="Y26" s="142"/>
+      <c r="Z26" s="142"/>
+      <c r="AA26" s="142"/>
+      <c r="AB26" s="142"/>
+      <c r="AC26" s="142"/>
+      <c r="AD26" s="142"/>
+      <c r="AE26" s="142"/>
+      <c r="AF26" s="142"/>
+      <c r="AG26" s="142"/>
+      <c r="AH26" s="142"/>
+      <c r="AI26" s="142"/>
     </row>
     <row r="27" spans="1:35" s="16" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="111" t="s">
+      <c r="A27" s="148" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" s="151" t="s">
         <v>67</v>
-      </c>
-      <c r="B27" s="114" t="s">
-        <v>68</v>
       </c>
       <c r="C27" s="22"/>
       <c r="D27" s="23"/>
@@ -3966,8 +3966,8 @@
       <c r="AI27" s="28"/>
     </row>
     <row r="28" spans="1:35" s="16" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="112"/>
-      <c r="B28" s="115"/>
+      <c r="A28" s="149"/>
+      <c r="B28" s="152"/>
       <c r="C28" s="22"/>
       <c r="D28" s="23"/>
       <c r="E28" s="28"/>
@@ -4003,8 +4003,8 @@
       <c r="AI28" s="28"/>
     </row>
     <row r="29" spans="1:35" s="16" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="113"/>
-      <c r="B29" s="116"/>
+      <c r="A29" s="150"/>
+      <c r="B29" s="153"/>
       <c r="C29" s="26" t="s">
         <v>53</v>
       </c>
@@ -4042,48 +4042,48 @@
       <c r="AI29" s="28"/>
     </row>
     <row r="30" spans="1:35" s="16" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="110"/>
-      <c r="B30" s="110"/>
-      <c r="C30" s="110"/>
-      <c r="D30" s="110"/>
-      <c r="E30" s="110"/>
-      <c r="F30" s="110"/>
-      <c r="G30" s="110"/>
-      <c r="H30" s="110"/>
-      <c r="I30" s="110"/>
-      <c r="J30" s="110"/>
-      <c r="K30" s="110"/>
-      <c r="L30" s="110"/>
-      <c r="M30" s="110"/>
-      <c r="N30" s="110"/>
-      <c r="O30" s="110"/>
-      <c r="P30" s="110"/>
-      <c r="Q30" s="110"/>
-      <c r="R30" s="110"/>
-      <c r="S30" s="110"/>
-      <c r="T30" s="110"/>
-      <c r="U30" s="110"/>
-      <c r="V30" s="110"/>
-      <c r="W30" s="110"/>
-      <c r="X30" s="110"/>
-      <c r="Y30" s="110"/>
-      <c r="Z30" s="110"/>
-      <c r="AA30" s="110"/>
-      <c r="AB30" s="110"/>
-      <c r="AC30" s="110"/>
-      <c r="AD30" s="110"/>
-      <c r="AE30" s="110"/>
-      <c r="AF30" s="110"/>
-      <c r="AG30" s="110"/>
-      <c r="AH30" s="110"/>
-      <c r="AI30" s="110"/>
+      <c r="A30" s="142"/>
+      <c r="B30" s="142"/>
+      <c r="C30" s="142"/>
+      <c r="D30" s="142"/>
+      <c r="E30" s="142"/>
+      <c r="F30" s="142"/>
+      <c r="G30" s="142"/>
+      <c r="H30" s="142"/>
+      <c r="I30" s="142"/>
+      <c r="J30" s="142"/>
+      <c r="K30" s="142"/>
+      <c r="L30" s="142"/>
+      <c r="M30" s="142"/>
+      <c r="N30" s="142"/>
+      <c r="O30" s="142"/>
+      <c r="P30" s="142"/>
+      <c r="Q30" s="142"/>
+      <c r="R30" s="142"/>
+      <c r="S30" s="142"/>
+      <c r="T30" s="142"/>
+      <c r="U30" s="142"/>
+      <c r="V30" s="142"/>
+      <c r="W30" s="142"/>
+      <c r="X30" s="142"/>
+      <c r="Y30" s="142"/>
+      <c r="Z30" s="142"/>
+      <c r="AA30" s="142"/>
+      <c r="AB30" s="142"/>
+      <c r="AC30" s="142"/>
+      <c r="AD30" s="142"/>
+      <c r="AE30" s="142"/>
+      <c r="AF30" s="142"/>
+      <c r="AG30" s="142"/>
+      <c r="AH30" s="142"/>
+      <c r="AI30" s="142"/>
     </row>
     <row r="31" spans="1:35" s="16" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="117" t="s">
-        <v>69</v>
-      </c>
-      <c r="B31" s="120" t="s">
-        <v>70</v>
+      <c r="A31" s="111" t="s">
+        <v>65</v>
+      </c>
+      <c r="B31" s="146" t="s">
+        <v>68</v>
       </c>
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
@@ -4120,8 +4120,8 @@
       <c r="AI31" s="27"/>
     </row>
     <row r="32" spans="1:35" s="16" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="118"/>
-      <c r="B32" s="121"/>
+      <c r="A32" s="112"/>
+      <c r="B32" s="114"/>
       <c r="C32" s="31"/>
       <c r="D32" s="23"/>
       <c r="E32" s="25"/>
@@ -4157,8 +4157,8 @@
       <c r="AI32" s="27"/>
     </row>
     <row r="33" spans="1:35" s="16" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="119"/>
-      <c r="B33" s="122"/>
+      <c r="A33" s="113"/>
+      <c r="B33" s="115"/>
       <c r="C33" s="31" t="s">
         <v>53</v>
       </c>
@@ -4195,7 +4195,7 @@
       <c r="AH33" s="23"/>
       <c r="AI33" s="23"/>
     </row>
-    <row r="34" spans="1:35" s="132" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="1:35" s="110" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" spans="1:35" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="32"/>
       <c r="D35" s="33"/>
@@ -4295,6 +4295,25 @@
     <protectedRange sqref="C11:C12 C15:C16" name="Range10_1"/>
   </protectedRanges>
   <mergeCells count="35">
+    <mergeCell ref="A26:AI26"/>
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="A30:AI30"/>
+    <mergeCell ref="A31:A33"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="A18:AI18"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="A14:AI14"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="D3:K5"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="L4:M4"/>
     <mergeCell ref="A34:XFD34"/>
     <mergeCell ref="A23:A25"/>
     <mergeCell ref="B23:B25"/>
@@ -4311,25 +4330,6 @@
     <mergeCell ref="A2:C6"/>
     <mergeCell ref="D2:K2"/>
     <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="D3:K5"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="A18:AI18"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="A14:AI14"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="A26:AI26"/>
-    <mergeCell ref="A27:A29"/>
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="A30:AI30"/>
-    <mergeCell ref="A31:A33"/>
-    <mergeCell ref="B31:B33"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.43307086614173002" right="0.43307086614173002" top="0.23622047244093999" bottom="0.23622047244093999" header="0.31496062992126" footer="0.31496062992126"/>
@@ -4358,83 +4358,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="81"/>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81" t="s">
-        <v>71</v>
-      </c>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81" t="s">
+      <c r="A1" s="89"/>
+      <c r="B1" s="89"/>
+      <c r="C1" s="89" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
+      <c r="H1" s="89"/>
+      <c r="I1" s="89"/>
+      <c r="J1" s="89"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="81"/>
-      <c r="B2" s="81"/>
-      <c r="C2" s="82" t="s">
+      <c r="A2" s="89"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="81" t="s">
+      <c r="D2" s="91"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="89" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="81"/>
-      <c r="B3" s="81"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="81" t="s">
+      <c r="A3" s="89"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="94"/>
+      <c r="G3" s="89" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="81"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="81"/>
-      <c r="B4" s="81"/>
-      <c r="C4" s="85"/>
-      <c r="D4" s="86"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="88" t="s">
-        <v>91</v>
-      </c>
-      <c r="H4" s="89"/>
-      <c r="I4" s="89"/>
-      <c r="J4" s="90"/>
+      <c r="A4" s="89"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="93"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="94"/>
+      <c r="G4" s="96" t="s">
+        <v>89</v>
+      </c>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="98"/>
     </row>
     <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="81"/>
-      <c r="B5" s="81"/>
+      <c r="A5" s="89"/>
+      <c r="B5" s="89"/>
       <c r="C5" s="154" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D5" s="155"/>
       <c r="E5" s="155"/>
       <c r="F5" s="155"/>
-      <c r="G5" s="91"/>
-      <c r="H5" s="92"/>
-      <c r="I5" s="92"/>
-      <c r="J5" s="93"/>
+      <c r="G5" s="99"/>
+      <c r="H5" s="100"/>
+      <c r="I5" s="100"/>
+      <c r="J5" s="101"/>
     </row>
     <row r="6" spans="1:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:10" s="16" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="156" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B7" s="156"/>
       <c r="C7" s="156"/>
@@ -4451,34 +4451,34 @@
     <row r="8" spans="1:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="1:10" s="38" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="36" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B9" s="36" t="s">
         <v>1</v>
       </c>
       <c r="C9" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" s="36" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="D9" s="36" t="s">
+      <c r="F9" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="E9" s="37" t="s">
+      <c r="G9" s="37" t="s">
         <v>77</v>
       </c>
-      <c r="F9" s="36" t="s">
+      <c r="H9" s="37" t="s">
         <v>78</v>
       </c>
-      <c r="G9" s="37" t="s">
+      <c r="I9" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="H9" s="37" t="s">
+      <c r="J9" s="37" t="s">
         <v>80</v>
-      </c>
-      <c r="I9" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="J9" s="37" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="38" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.25">
@@ -5024,99 +5024,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="81"/>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81" t="s">
-        <v>71</v>
-      </c>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="127"/>
-      <c r="G1" s="81" t="s">
+      <c r="A1" s="89"/>
+      <c r="B1" s="89"/>
+      <c r="C1" s="89" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
+      <c r="H1" s="89"/>
+      <c r="I1" s="89"/>
+      <c r="J1" s="89"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="81"/>
-      <c r="B2" s="81"/>
-      <c r="C2" s="82" t="s">
+      <c r="A2" s="89"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="81" t="s">
+      <c r="D2" s="91"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="89" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="81"/>
-      <c r="B3" s="81"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="81" t="s">
+      <c r="A3" s="89"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="94"/>
+      <c r="G3" s="89" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="81"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="81"/>
-      <c r="B4" s="81"/>
-      <c r="C4" s="85"/>
-      <c r="D4" s="86"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="88" t="s">
-        <v>90</v>
-      </c>
-      <c r="H4" s="89"/>
-      <c r="I4" s="89"/>
-      <c r="J4" s="90"/>
+      <c r="A4" s="89"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="93"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="94"/>
+      <c r="G4" s="96" t="s">
+        <v>88</v>
+      </c>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="98"/>
     </row>
     <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="81"/>
-      <c r="B5" s="81"/>
+      <c r="A5" s="89"/>
+      <c r="B5" s="89"/>
       <c r="C5" s="154" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D5" s="155"/>
       <c r="E5" s="155"/>
       <c r="F5" s="155"/>
-      <c r="G5" s="165"/>
-      <c r="H5" s="73"/>
-      <c r="I5" s="73"/>
-      <c r="J5" s="166"/>
+      <c r="G5" s="158"/>
+      <c r="H5" s="109"/>
+      <c r="I5" s="109"/>
+      <c r="J5" s="159"/>
     </row>
     <row r="6" spans="1:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="62"/>
-      <c r="G6" s="165"/>
-      <c r="H6" s="73"/>
-      <c r="I6" s="73"/>
-      <c r="J6" s="166"/>
+      <c r="G6" s="158"/>
+      <c r="H6" s="109"/>
+      <c r="I6" s="109"/>
+      <c r="J6" s="159"/>
     </row>
     <row r="7" spans="1:10" s="16" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="161" t="s">
-        <v>73</v>
+      <c r="A7" s="163" t="s">
+        <v>71</v>
       </c>
       <c r="B7" s="156"/>
       <c r="C7" s="156"/>
       <c r="D7" s="156"/>
       <c r="E7" s="156"/>
       <c r="F7" s="35"/>
-      <c r="G7" s="165"/>
-      <c r="H7" s="73"/>
-      <c r="I7" s="73"/>
-      <c r="J7" s="166"/>
+      <c r="G7" s="158"/>
+      <c r="H7" s="109"/>
+      <c r="I7" s="109"/>
+      <c r="J7" s="159"/>
     </row>
     <row r="8" spans="1:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="62"/>
@@ -5125,29 +5125,29 @@
     </row>
     <row r="9" spans="1:10" s="38" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="36" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B9" s="36" t="s">
         <v>1</v>
       </c>
       <c r="C9" s="36" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D9" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="E9" s="64" t="s">
+        <v>85</v>
+      </c>
+      <c r="F9" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="E9" s="64" t="s">
+      <c r="G9" s="164" t="s">
         <v>87</v>
       </c>
-      <c r="F9" s="65" t="s">
-        <v>88</v>
-      </c>
-      <c r="G9" s="162" t="s">
-        <v>89</v>
-      </c>
-      <c r="H9" s="163"/>
-      <c r="I9" s="163"/>
-      <c r="J9" s="164"/>
+      <c r="H9" s="165"/>
+      <c r="I9" s="165"/>
+      <c r="J9" s="166"/>
     </row>
     <row r="10" spans="1:10" s="38" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
@@ -5158,10 +5158,10 @@
       <c r="D10" s="41"/>
       <c r="E10" s="66"/>
       <c r="F10" s="67"/>
-      <c r="G10" s="158"/>
-      <c r="H10" s="159"/>
-      <c r="I10" s="159"/>
-      <c r="J10" s="160"/>
+      <c r="G10" s="160"/>
+      <c r="H10" s="161"/>
+      <c r="I10" s="161"/>
+      <c r="J10" s="162"/>
     </row>
     <row r="11" spans="1:10" s="38" customFormat="1" ht="136.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10">
@@ -5172,10 +5172,10 @@
       <c r="D11" s="43"/>
       <c r="E11" s="66"/>
       <c r="F11" s="68"/>
-      <c r="G11" s="159"/>
-      <c r="H11" s="159"/>
-      <c r="I11" s="159"/>
-      <c r="J11" s="160"/>
+      <c r="G11" s="161"/>
+      <c r="H11" s="161"/>
+      <c r="I11" s="161"/>
+      <c r="J11" s="162"/>
     </row>
     <row r="12" spans="1:10" s="38" customFormat="1" ht="138" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
@@ -5186,10 +5186,10 @@
       <c r="D12" s="43"/>
       <c r="E12" s="69"/>
       <c r="F12" s="70"/>
-      <c r="G12" s="158"/>
-      <c r="H12" s="159"/>
-      <c r="I12" s="159"/>
-      <c r="J12" s="160"/>
+      <c r="G12" s="160"/>
+      <c r="H12" s="161"/>
+      <c r="I12" s="161"/>
+      <c r="J12" s="162"/>
     </row>
     <row r="13" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10">
@@ -5200,10 +5200,10 @@
       <c r="D13" s="42"/>
       <c r="E13" s="69"/>
       <c r="F13" s="70"/>
-      <c r="G13" s="158"/>
-      <c r="H13" s="159"/>
-      <c r="I13" s="159"/>
-      <c r="J13" s="160"/>
+      <c r="G13" s="160"/>
+      <c r="H13" s="161"/>
+      <c r="I13" s="161"/>
+      <c r="J13" s="162"/>
     </row>
     <row r="14" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
@@ -5214,10 +5214,10 @@
       <c r="D14" s="42"/>
       <c r="E14" s="66"/>
       <c r="F14" s="67"/>
-      <c r="G14" s="158"/>
-      <c r="H14" s="159"/>
-      <c r="I14" s="159"/>
-      <c r="J14" s="160"/>
+      <c r="G14" s="160"/>
+      <c r="H14" s="161"/>
+      <c r="I14" s="161"/>
+      <c r="J14" s="162"/>
     </row>
     <row r="15" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10">
@@ -5228,10 +5228,10 @@
       <c r="D15" s="42"/>
       <c r="E15" s="69"/>
       <c r="F15" s="71"/>
-      <c r="G15" s="159"/>
-      <c r="H15" s="159"/>
-      <c r="I15" s="159"/>
-      <c r="J15" s="160"/>
+      <c r="G15" s="161"/>
+      <c r="H15" s="161"/>
+      <c r="I15" s="161"/>
+      <c r="J15" s="162"/>
     </row>
     <row r="16" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10">
@@ -5242,10 +5242,10 @@
       <c r="D16" s="42"/>
       <c r="E16" s="69"/>
       <c r="F16" s="70"/>
-      <c r="G16" s="158"/>
-      <c r="H16" s="159"/>
-      <c r="I16" s="159"/>
-      <c r="J16" s="160"/>
+      <c r="G16" s="160"/>
+      <c r="H16" s="161"/>
+      <c r="I16" s="161"/>
+      <c r="J16" s="162"/>
     </row>
     <row r="17" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
@@ -5256,10 +5256,10 @@
       <c r="D17" s="42"/>
       <c r="E17" s="69"/>
       <c r="F17" s="70"/>
-      <c r="G17" s="158"/>
-      <c r="H17" s="159"/>
-      <c r="I17" s="159"/>
-      <c r="J17" s="160"/>
+      <c r="G17" s="160"/>
+      <c r="H17" s="161"/>
+      <c r="I17" s="161"/>
+      <c r="J17" s="162"/>
     </row>
     <row r="18" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
@@ -5270,10 +5270,10 @@
       <c r="D18" s="42"/>
       <c r="E18" s="69"/>
       <c r="F18" s="70"/>
-      <c r="G18" s="158"/>
-      <c r="H18" s="159"/>
-      <c r="I18" s="159"/>
-      <c r="J18" s="160"/>
+      <c r="G18" s="160"/>
+      <c r="H18" s="161"/>
+      <c r="I18" s="161"/>
+      <c r="J18" s="162"/>
     </row>
     <row r="19" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10">
@@ -5284,10 +5284,10 @@
       <c r="D19" s="42"/>
       <c r="E19" s="69"/>
       <c r="F19" s="70"/>
-      <c r="G19" s="158"/>
-      <c r="H19" s="159"/>
-      <c r="I19" s="159"/>
-      <c r="J19" s="160"/>
+      <c r="G19" s="160"/>
+      <c r="H19" s="161"/>
+      <c r="I19" s="161"/>
+      <c r="J19" s="162"/>
     </row>
     <row r="20" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
@@ -5298,10 +5298,10 @@
       <c r="D20" s="42"/>
       <c r="E20" s="69"/>
       <c r="F20" s="70"/>
-      <c r="G20" s="158"/>
-      <c r="H20" s="159"/>
-      <c r="I20" s="159"/>
-      <c r="J20" s="160"/>
+      <c r="G20" s="160"/>
+      <c r="H20" s="161"/>
+      <c r="I20" s="161"/>
+      <c r="J20" s="162"/>
     </row>
     <row r="21" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10">
@@ -5312,10 +5312,10 @@
       <c r="D21" s="42"/>
       <c r="E21" s="69"/>
       <c r="F21" s="70"/>
-      <c r="G21" s="158"/>
-      <c r="H21" s="159"/>
-      <c r="I21" s="159"/>
-      <c r="J21" s="160"/>
+      <c r="G21" s="160"/>
+      <c r="H21" s="161"/>
+      <c r="I21" s="161"/>
+      <c r="J21" s="162"/>
     </row>
     <row r="22" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
@@ -5326,10 +5326,10 @@
       <c r="D22" s="42"/>
       <c r="E22" s="69"/>
       <c r="F22" s="70"/>
-      <c r="G22" s="158"/>
-      <c r="H22" s="159"/>
-      <c r="I22" s="159"/>
-      <c r="J22" s="160"/>
+      <c r="G22" s="160"/>
+      <c r="H22" s="161"/>
+      <c r="I22" s="161"/>
+      <c r="J22" s="162"/>
     </row>
     <row r="23" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10">
@@ -5340,10 +5340,10 @@
       <c r="D23" s="42"/>
       <c r="E23" s="69"/>
       <c r="F23" s="70"/>
-      <c r="G23" s="158"/>
-      <c r="H23" s="159"/>
-      <c r="I23" s="159"/>
-      <c r="J23" s="160"/>
+      <c r="G23" s="160"/>
+      <c r="H23" s="161"/>
+      <c r="I23" s="161"/>
+      <c r="J23" s="162"/>
     </row>
     <row r="24" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
@@ -5354,10 +5354,10 @@
       <c r="D24" s="42"/>
       <c r="E24" s="69"/>
       <c r="F24" s="70"/>
-      <c r="G24" s="158"/>
-      <c r="H24" s="159"/>
-      <c r="I24" s="159"/>
-      <c r="J24" s="160"/>
+      <c r="G24" s="160"/>
+      <c r="H24" s="161"/>
+      <c r="I24" s="161"/>
+      <c r="J24" s="162"/>
     </row>
     <row r="25" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10">
@@ -5368,10 +5368,10 @@
       <c r="D25" s="42"/>
       <c r="E25" s="69"/>
       <c r="F25" s="70"/>
-      <c r="G25" s="158"/>
-      <c r="H25" s="159"/>
-      <c r="I25" s="159"/>
-      <c r="J25" s="160"/>
+      <c r="G25" s="160"/>
+      <c r="H25" s="161"/>
+      <c r="I25" s="161"/>
+      <c r="J25" s="162"/>
     </row>
     <row r="26" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
@@ -5382,10 +5382,10 @@
       <c r="D26" s="42"/>
       <c r="E26" s="69"/>
       <c r="F26" s="70"/>
-      <c r="G26" s="158"/>
-      <c r="H26" s="159"/>
-      <c r="I26" s="159"/>
-      <c r="J26" s="160"/>
+      <c r="G26" s="160"/>
+      <c r="H26" s="161"/>
+      <c r="I26" s="161"/>
+      <c r="J26" s="162"/>
     </row>
     <row r="27" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10">
@@ -5396,10 +5396,10 @@
       <c r="D27" s="42"/>
       <c r="E27" s="69"/>
       <c r="F27" s="70"/>
-      <c r="G27" s="158"/>
-      <c r="H27" s="159"/>
-      <c r="I27" s="159"/>
-      <c r="J27" s="160"/>
+      <c r="G27" s="160"/>
+      <c r="H27" s="161"/>
+      <c r="I27" s="161"/>
+      <c r="J27" s="162"/>
     </row>
     <row r="28" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="10">
@@ -5410,10 +5410,10 @@
       <c r="D28" s="42"/>
       <c r="E28" s="69"/>
       <c r="F28" s="70"/>
-      <c r="G28" s="158"/>
-      <c r="H28" s="159"/>
-      <c r="I28" s="159"/>
-      <c r="J28" s="160"/>
+      <c r="G28" s="160"/>
+      <c r="H28" s="161"/>
+      <c r="I28" s="161"/>
+      <c r="J28" s="162"/>
     </row>
     <row r="29" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10">
@@ -5424,10 +5424,10 @@
       <c r="D29" s="42"/>
       <c r="E29" s="69"/>
       <c r="F29" s="70"/>
-      <c r="G29" s="158"/>
-      <c r="H29" s="159"/>
-      <c r="I29" s="159"/>
-      <c r="J29" s="160"/>
+      <c r="G29" s="160"/>
+      <c r="H29" s="161"/>
+      <c r="I29" s="161"/>
+      <c r="J29" s="162"/>
     </row>
     <row r="30" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="10">
@@ -5438,10 +5438,10 @@
       <c r="D30" s="42"/>
       <c r="E30" s="69"/>
       <c r="F30" s="70"/>
-      <c r="G30" s="158"/>
-      <c r="H30" s="159"/>
-      <c r="I30" s="159"/>
-      <c r="J30" s="160"/>
+      <c r="G30" s="160"/>
+      <c r="H30" s="161"/>
+      <c r="I30" s="161"/>
+      <c r="J30" s="162"/>
     </row>
     <row r="31" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10">
@@ -5452,10 +5452,10 @@
       <c r="D31" s="42"/>
       <c r="E31" s="69"/>
       <c r="F31" s="70"/>
-      <c r="G31" s="158"/>
-      <c r="H31" s="159"/>
-      <c r="I31" s="159"/>
-      <c r="J31" s="160"/>
+      <c r="G31" s="160"/>
+      <c r="H31" s="161"/>
+      <c r="I31" s="161"/>
+      <c r="J31" s="162"/>
     </row>
     <row r="32" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="10">
@@ -5466,10 +5466,10 @@
       <c r="D32" s="42"/>
       <c r="E32" s="69"/>
       <c r="F32" s="70"/>
-      <c r="G32" s="158"/>
-      <c r="H32" s="159"/>
-      <c r="I32" s="159"/>
-      <c r="J32" s="160"/>
+      <c r="G32" s="160"/>
+      <c r="H32" s="161"/>
+      <c r="I32" s="161"/>
+      <c r="J32" s="162"/>
     </row>
     <row r="33" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10">
@@ -5480,10 +5480,10 @@
       <c r="D33" s="42"/>
       <c r="E33" s="69"/>
       <c r="F33" s="70"/>
-      <c r="G33" s="158"/>
-      <c r="H33" s="159"/>
-      <c r="I33" s="159"/>
-      <c r="J33" s="160"/>
+      <c r="G33" s="160"/>
+      <c r="H33" s="161"/>
+      <c r="I33" s="161"/>
+      <c r="J33" s="162"/>
     </row>
     <row r="34" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="10">
@@ -5494,10 +5494,10 @@
       <c r="D34" s="42"/>
       <c r="E34" s="69"/>
       <c r="F34" s="70"/>
-      <c r="G34" s="158"/>
-      <c r="H34" s="159"/>
-      <c r="I34" s="159"/>
-      <c r="J34" s="160"/>
+      <c r="G34" s="160"/>
+      <c r="H34" s="161"/>
+      <c r="I34" s="161"/>
+      <c r="J34" s="162"/>
     </row>
     <row r="35" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10">
@@ -5508,10 +5508,10 @@
       <c r="D35" s="42"/>
       <c r="E35" s="69"/>
       <c r="F35" s="70"/>
-      <c r="G35" s="158"/>
-      <c r="H35" s="159"/>
-      <c r="I35" s="159"/>
-      <c r="J35" s="160"/>
+      <c r="G35" s="160"/>
+      <c r="H35" s="161"/>
+      <c r="I35" s="161"/>
+      <c r="J35" s="162"/>
     </row>
     <row r="36" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="10">
@@ -5522,10 +5522,10 @@
       <c r="D36" s="42"/>
       <c r="E36" s="69"/>
       <c r="F36" s="70"/>
-      <c r="G36" s="158"/>
-      <c r="H36" s="159"/>
-      <c r="I36" s="159"/>
-      <c r="J36" s="160"/>
+      <c r="G36" s="160"/>
+      <c r="H36" s="161"/>
+      <c r="I36" s="161"/>
+      <c r="J36" s="162"/>
     </row>
     <row r="37" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10">
@@ -5536,10 +5536,10 @@
       <c r="D37" s="42"/>
       <c r="E37" s="69"/>
       <c r="F37" s="70"/>
-      <c r="G37" s="158"/>
-      <c r="H37" s="159"/>
-      <c r="I37" s="159"/>
-      <c r="J37" s="160"/>
+      <c r="G37" s="160"/>
+      <c r="H37" s="161"/>
+      <c r="I37" s="161"/>
+      <c r="J37" s="162"/>
     </row>
     <row r="38" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="10">
@@ -5550,10 +5550,10 @@
       <c r="D38" s="42"/>
       <c r="E38" s="69"/>
       <c r="F38" s="70"/>
-      <c r="G38" s="158"/>
-      <c r="H38" s="159"/>
-      <c r="I38" s="159"/>
-      <c r="J38" s="160"/>
+      <c r="G38" s="160"/>
+      <c r="H38" s="161"/>
+      <c r="I38" s="161"/>
+      <c r="J38" s="162"/>
     </row>
     <row r="39" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10">
@@ -5564,10 +5564,10 @@
       <c r="D39" s="42"/>
       <c r="E39" s="69"/>
       <c r="F39" s="70"/>
-      <c r="G39" s="158"/>
-      <c r="H39" s="159"/>
-      <c r="I39" s="159"/>
-      <c r="J39" s="160"/>
+      <c r="G39" s="160"/>
+      <c r="H39" s="161"/>
+      <c r="I39" s="161"/>
+      <c r="J39" s="162"/>
     </row>
     <row r="40" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="10">
@@ -5578,10 +5578,10 @@
       <c r="D40" s="42"/>
       <c r="E40" s="69"/>
       <c r="F40" s="70"/>
-      <c r="G40" s="158"/>
-      <c r="H40" s="159"/>
-      <c r="I40" s="159"/>
-      <c r="J40" s="160"/>
+      <c r="G40" s="160"/>
+      <c r="H40" s="161"/>
+      <c r="I40" s="161"/>
+      <c r="J40" s="162"/>
     </row>
     <row r="41" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="10">
@@ -5592,10 +5592,10 @@
       <c r="D41" s="42"/>
       <c r="E41" s="69"/>
       <c r="F41" s="70"/>
-      <c r="G41" s="158"/>
-      <c r="H41" s="159"/>
-      <c r="I41" s="159"/>
-      <c r="J41" s="160"/>
+      <c r="G41" s="160"/>
+      <c r="H41" s="161"/>
+      <c r="I41" s="161"/>
+      <c r="J41" s="162"/>
     </row>
     <row r="42" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="10">
@@ -5606,10 +5606,10 @@
       <c r="D42" s="42"/>
       <c r="E42" s="69"/>
       <c r="F42" s="70"/>
-      <c r="G42" s="158"/>
-      <c r="H42" s="159"/>
-      <c r="I42" s="159"/>
-      <c r="J42" s="160"/>
+      <c r="G42" s="160"/>
+      <c r="H42" s="161"/>
+      <c r="I42" s="161"/>
+      <c r="J42" s="162"/>
     </row>
     <row r="43" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="10">
@@ -5620,10 +5620,10 @@
       <c r="D43" s="42"/>
       <c r="E43" s="69"/>
       <c r="F43" s="70"/>
-      <c r="G43" s="158"/>
-      <c r="H43" s="159"/>
-      <c r="I43" s="159"/>
-      <c r="J43" s="160"/>
+      <c r="G43" s="160"/>
+      <c r="H43" s="161"/>
+      <c r="I43" s="161"/>
+      <c r="J43" s="162"/>
     </row>
     <row r="44" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="10">
@@ -5634,10 +5634,10 @@
       <c r="D44" s="42"/>
       <c r="E44" s="69"/>
       <c r="F44" s="70"/>
-      <c r="G44" s="158"/>
-      <c r="H44" s="159"/>
-      <c r="I44" s="159"/>
-      <c r="J44" s="160"/>
+      <c r="G44" s="160"/>
+      <c r="H44" s="161"/>
+      <c r="I44" s="161"/>
+      <c r="J44" s="162"/>
     </row>
     <row r="45" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10">
@@ -5648,10 +5648,10 @@
       <c r="D45" s="42"/>
       <c r="E45" s="69"/>
       <c r="F45" s="70"/>
-      <c r="G45" s="158"/>
-      <c r="H45" s="159"/>
-      <c r="I45" s="159"/>
-      <c r="J45" s="160"/>
+      <c r="G45" s="160"/>
+      <c r="H45" s="161"/>
+      <c r="I45" s="161"/>
+      <c r="J45" s="162"/>
     </row>
     <row r="46" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="10">
@@ -5662,10 +5662,10 @@
       <c r="D46" s="42"/>
       <c r="E46" s="69"/>
       <c r="F46" s="70"/>
-      <c r="G46" s="158"/>
-      <c r="H46" s="159"/>
-      <c r="I46" s="159"/>
-      <c r="J46" s="160"/>
+      <c r="G46" s="160"/>
+      <c r="H46" s="161"/>
+      <c r="I46" s="161"/>
+      <c r="J46" s="162"/>
     </row>
     <row r="47" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10">
@@ -5676,10 +5676,10 @@
       <c r="D47" s="42"/>
       <c r="E47" s="69"/>
       <c r="F47" s="70"/>
-      <c r="G47" s="158"/>
-      <c r="H47" s="159"/>
-      <c r="I47" s="159"/>
-      <c r="J47" s="160"/>
+      <c r="G47" s="160"/>
+      <c r="H47" s="161"/>
+      <c r="I47" s="161"/>
+      <c r="J47" s="162"/>
     </row>
     <row r="48" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="10">
@@ -5690,10 +5690,10 @@
       <c r="D48" s="42"/>
       <c r="E48" s="69"/>
       <c r="F48" s="70"/>
-      <c r="G48" s="158"/>
-      <c r="H48" s="159"/>
-      <c r="I48" s="159"/>
-      <c r="J48" s="160"/>
+      <c r="G48" s="160"/>
+      <c r="H48" s="161"/>
+      <c r="I48" s="161"/>
+      <c r="J48" s="162"/>
     </row>
     <row r="49" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10">
@@ -5704,10 +5704,10 @@
       <c r="D49" s="42"/>
       <c r="E49" s="69"/>
       <c r="F49" s="70"/>
-      <c r="G49" s="158"/>
-      <c r="H49" s="159"/>
-      <c r="I49" s="159"/>
-      <c r="J49" s="160"/>
+      <c r="G49" s="160"/>
+      <c r="H49" s="161"/>
+      <c r="I49" s="161"/>
+      <c r="J49" s="162"/>
     </row>
     <row r="50" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="10">
@@ -5718,10 +5718,10 @@
       <c r="D50" s="42"/>
       <c r="E50" s="69"/>
       <c r="F50" s="70"/>
-      <c r="G50" s="158"/>
-      <c r="H50" s="159"/>
-      <c r="I50" s="159"/>
-      <c r="J50" s="160"/>
+      <c r="G50" s="160"/>
+      <c r="H50" s="161"/>
+      <c r="I50" s="161"/>
+      <c r="J50" s="162"/>
     </row>
     <row r="51" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10">
@@ -5732,10 +5732,10 @@
       <c r="D51" s="42"/>
       <c r="E51" s="69"/>
       <c r="F51" s="70"/>
-      <c r="G51" s="158"/>
-      <c r="H51" s="159"/>
-      <c r="I51" s="159"/>
-      <c r="J51" s="160"/>
+      <c r="G51" s="160"/>
+      <c r="H51" s="161"/>
+      <c r="I51" s="161"/>
+      <c r="J51" s="162"/>
     </row>
     <row r="52" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="10">
@@ -5746,10 +5746,10 @@
       <c r="D52" s="42"/>
       <c r="E52" s="69"/>
       <c r="F52" s="70"/>
-      <c r="G52" s="158"/>
-      <c r="H52" s="159"/>
-      <c r="I52" s="159"/>
-      <c r="J52" s="160"/>
+      <c r="G52" s="160"/>
+      <c r="H52" s="161"/>
+      <c r="I52" s="161"/>
+      <c r="J52" s="162"/>
     </row>
     <row r="53" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10">
@@ -5760,10 +5760,10 @@
       <c r="D53" s="42"/>
       <c r="E53" s="69"/>
       <c r="F53" s="70"/>
-      <c r="G53" s="158"/>
-      <c r="H53" s="159"/>
-      <c r="I53" s="159"/>
-      <c r="J53" s="160"/>
+      <c r="G53" s="160"/>
+      <c r="H53" s="161"/>
+      <c r="I53" s="161"/>
+      <c r="J53" s="162"/>
     </row>
     <row r="54" spans="1:10" s="38" customFormat="1" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="10">
@@ -5774,10 +5774,10 @@
       <c r="D54" s="46"/>
       <c r="E54" s="69"/>
       <c r="F54" s="70"/>
-      <c r="G54" s="158"/>
-      <c r="H54" s="159"/>
-      <c r="I54" s="159"/>
-      <c r="J54" s="160"/>
+      <c r="G54" s="160"/>
+      <c r="H54" s="161"/>
+      <c r="I54" s="161"/>
+      <c r="J54" s="162"/>
     </row>
     <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="60" spans="1:10" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5789,6 +5789,48 @@
     <protectedRange sqref="E11 E14 B13:D54 E15:F54 D10:D12 E10:F10 E12:F13 G10:J54" name="Range1"/>
   </protectedRanges>
   <mergeCells count="58">
+    <mergeCell ref="G52:J52"/>
+    <mergeCell ref="G53:J53"/>
+    <mergeCell ref="G46:J46"/>
+    <mergeCell ref="G47:J47"/>
+    <mergeCell ref="G48:J48"/>
+    <mergeCell ref="G49:J49"/>
+    <mergeCell ref="G50:J50"/>
+    <mergeCell ref="G51:J51"/>
+    <mergeCell ref="G32:J32"/>
+    <mergeCell ref="G45:J45"/>
+    <mergeCell ref="G34:J34"/>
+    <mergeCell ref="G35:J35"/>
+    <mergeCell ref="G36:J36"/>
+    <mergeCell ref="G37:J37"/>
+    <mergeCell ref="G38:J38"/>
+    <mergeCell ref="G39:J39"/>
+    <mergeCell ref="G40:J40"/>
+    <mergeCell ref="G41:J41"/>
+    <mergeCell ref="G42:J42"/>
+    <mergeCell ref="G43:J43"/>
+    <mergeCell ref="G44:J44"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="G33:J33"/>
+    <mergeCell ref="G54:J54"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="G22:J22"/>
+    <mergeCell ref="G23:J23"/>
+    <mergeCell ref="G24:J24"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="G26:J26"/>
+    <mergeCell ref="G27:J27"/>
+    <mergeCell ref="G28:J28"/>
+    <mergeCell ref="G29:J29"/>
+    <mergeCell ref="G30:J30"/>
+    <mergeCell ref="G31:J31"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="G13:J13"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="G15:J15"/>
+    <mergeCell ref="G16:J16"/>
     <mergeCell ref="G4:J7"/>
     <mergeCell ref="G18:J18"/>
     <mergeCell ref="C5:F5"/>
@@ -5805,48 +5847,6 @@
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="G13:J13"/>
-    <mergeCell ref="G14:J14"/>
-    <mergeCell ref="G15:J15"/>
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="G33:J33"/>
-    <mergeCell ref="G54:J54"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="G22:J22"/>
-    <mergeCell ref="G23:J23"/>
-    <mergeCell ref="G24:J24"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="G26:J26"/>
-    <mergeCell ref="G27:J27"/>
-    <mergeCell ref="G28:J28"/>
-    <mergeCell ref="G29:J29"/>
-    <mergeCell ref="G30:J30"/>
-    <mergeCell ref="G31:J31"/>
-    <mergeCell ref="G32:J32"/>
-    <mergeCell ref="G45:J45"/>
-    <mergeCell ref="G34:J34"/>
-    <mergeCell ref="G35:J35"/>
-    <mergeCell ref="G36:J36"/>
-    <mergeCell ref="G37:J37"/>
-    <mergeCell ref="G38:J38"/>
-    <mergeCell ref="G39:J39"/>
-    <mergeCell ref="G40:J40"/>
-    <mergeCell ref="G41:J41"/>
-    <mergeCell ref="G42:J42"/>
-    <mergeCell ref="G43:J43"/>
-    <mergeCell ref="G44:J44"/>
-    <mergeCell ref="G52:J52"/>
-    <mergeCell ref="G53:J53"/>
-    <mergeCell ref="G46:J46"/>
-    <mergeCell ref="G47:J47"/>
-    <mergeCell ref="G48:J48"/>
-    <mergeCell ref="G49:J49"/>
-    <mergeCell ref="G50:J50"/>
-    <mergeCell ref="G51:J51"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.43307086614173002" right="0.43307086614173002" top="0.51181102362205" bottom="0.31496062992126" header="0.31496062992126" footer="0.31496062992126"/>
